--- a/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
@@ -517,6 +517,9 @@
       <c r="C11" t="str">
         <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F11" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -575,7 +578,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010105151557550</v>
+        <v>0101051515575515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,9 +521,92 @@
         <v>15</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>863_干花文竹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F15" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>104_绣球重瓣紫_Hydrangea Purple D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101051515575515</v>
+        <v>0101051515575515102020202020305100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101051515575515102020202020305100</v>
+        <v>01010515155755151020202020203051015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,89 @@
         <v>15</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>744_永生吊米深红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>707_永生吊米白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4</v>
+      </c>
+      <c r="C24" t="str">
+        <v>763_芍药独家记忆_undefined_undefined_10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>493_咖喱花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>819_中华桔梗白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>818_八卦草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +744,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010515155755151020202020203051015</v>
+        <v>01010515155755151020202020203051015101050205451050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-21.xlsx
@@ -686,6 +686,9 @@
       <c r="C31" t="str">
         <v>770_弯葱_undefined_undefined_10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -744,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010515155755151020202020203051015101050205451050</v>
+        <v>010105151557551510202020202030510151010502054510520</v>
       </c>
     </row>
   </sheetData>
